--- a/Dados.xlsx
+++ b/Dados.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hebertribeiro/Laudo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hebertribeiro/laudo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536B657F-77CE-2849-BA84-E52D058D78A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E285AEA6-866E-9E45-90DF-1E059CE057FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="320" yWindow="600" windowWidth="24940" windowHeight="13920" xr2:uid="{FD95C108-172A-DC44-AC56-6F3CF0C86573}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="52">
   <si>
     <t>Cliente/Fazenda</t>
   </si>
@@ -71,33 +71,6 @@
     <t>Willian Matté - Grupo MEC</t>
   </si>
   <si>
-    <t>Laboratorista</t>
-  </si>
-  <si>
-    <t>Hebert</t>
-  </si>
-  <si>
-    <t>Danilo</t>
-  </si>
-  <si>
-    <t>Moises</t>
-  </si>
-  <si>
-    <t>Vitor</t>
-  </si>
-  <si>
-    <t>Gean</t>
-  </si>
-  <si>
-    <t>Esther</t>
-  </si>
-  <si>
-    <t>Julianna/Hellen</t>
-  </si>
-  <si>
-    <t>Naiara</t>
-  </si>
-  <si>
     <t>Nome do Produto</t>
   </si>
   <si>
@@ -146,30 +119,6 @@
     <t>Meio de Cultura</t>
   </si>
   <si>
-    <t>Solufarm SH</t>
-  </si>
-  <si>
-    <t>Solufarm Bac</t>
-  </si>
-  <si>
-    <t>Solufarm Bug</t>
-  </si>
-  <si>
-    <t>Solufarm Catp</t>
-  </si>
-  <si>
-    <t>Solufarm RZB</t>
-  </si>
-  <si>
-    <t>Solufarm AZ</t>
-  </si>
-  <si>
-    <t>Solufarm White</t>
-  </si>
-  <si>
-    <t>Solufarm Isaria</t>
-  </si>
-  <si>
     <t>Bacillus amyloliquefaciens</t>
   </si>
   <si>
@@ -194,9 +143,6 @@
     <t>Bacillus velezensis</t>
   </si>
   <si>
-    <t>Beauveria bassian</t>
-  </si>
-  <si>
     <t>Azospirillum brasilense</t>
   </si>
   <si>
@@ -218,7 +164,37 @@
     <t xml:space="preserve">Tec Isaria </t>
   </si>
   <si>
-    <t>Solufarm SM</t>
+    <t>Beauveria bassiana</t>
+  </si>
+  <si>
+    <t>SH</t>
+  </si>
+  <si>
+    <t>BAC</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>BUG</t>
+  </si>
+  <si>
+    <t>CATP</t>
+  </si>
+  <si>
+    <t>BCA</t>
+  </si>
+  <si>
+    <t>RZB</t>
+  </si>
+  <si>
+    <t>AZ</t>
+  </si>
+  <si>
+    <t>WHITE</t>
+  </si>
+  <si>
+    <t>ISARIA</t>
   </si>
 </sst>
 </file>
@@ -616,249 +592,221 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C9A3EEC-BDB8-E54E-A0B0-19087A08BEBC}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="4" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="4" customFormat="1" ht="22" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="D1" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="E1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" t="s">
         <v>50</v>
       </c>
-      <c r="G10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E13" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E14" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" t="s">
+    </row>
+    <row r="16" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="C16" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E15" t="s">
-        <v>57</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="D16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" t="s">
         <v>51</v>
-      </c>
-      <c r="G15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="E16" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G16" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
